--- a/sources/michelle_step6.xlsx
+++ b/sources/michelle_step6.xlsx
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Launching Shuttle [~5]</t>
+          <t>Launching Shuttle [Tag]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">

--- a/sources/michelle_step6.xlsx
+++ b/sources/michelle_step6.xlsx
@@ -722,6 +722,11 @@
           <t>Special Tag Throw with Julia only. Julia finishes with a Running Bulldog. Total damage is 12,24.</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
@@ -759,6 +764,11 @@
           <t>d</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
@@ -811,6 +821,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
@@ -858,6 +873,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
@@ -903,6 +923,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>e0cf556a-57d8-4762-b577-f4d445bc558f</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -5746,6 +5771,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
@@ -5778,6 +5808,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
+        </is>
+      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
@@ -5808,6 +5843,11 @@
       <c r="K102" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>04575a0d-bb87-4254-a98a-681589f81afc</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
